--- a/scenarios/Coal_Flexibilisation/sub_scenarios/fixed_technologies.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/fixed_technologies.xlsx
@@ -1264,9 +1264,8 @@
       <c r="K2" s="93" t="n">
         <v>13.54166666666667</v>
       </c>
-      <c r="L2" s="94">
-        <f>K2</f>
-        <v/>
+      <c r="L2" s="94" t="n">
+        <v>13.54166666666667</v>
       </c>
       <c r="M2" s="52" t="n">
         <v>0</v>
@@ -1327,9 +1326,10 @@
       <c r="AE2" s="19" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="71">
-        <f>A2</f>
-        <v/>
+      <c r="A3" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
@@ -1369,9 +1369,8 @@
       <c r="K3" s="98" t="n">
         <v>14.375</v>
       </c>
-      <c r="L3" s="94">
-        <f>K3</f>
-        <v/>
+      <c r="L3" s="94" t="n">
+        <v>14.375</v>
       </c>
       <c r="M3" s="52" t="n">
         <v>0</v>
@@ -1432,9 +1431,10 @@
       <c r="AE3" s="19" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="71">
-        <f>A3</f>
-        <v/>
+      <c r="A4" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
@@ -1474,9 +1474,8 @@
       <c r="K4" s="98" t="n">
         <v>11.66666666666667</v>
       </c>
-      <c r="L4" s="94">
-        <f>K4</f>
-        <v/>
+      <c r="L4" s="94" t="n">
+        <v>11.66666666666667</v>
       </c>
       <c r="M4" s="52" t="n">
         <v>0</v>
@@ -1537,9 +1536,10 @@
       <c r="AE4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="71">
-        <f>A4</f>
-        <v/>
+      <c r="A5" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
@@ -1579,9 +1579,8 @@
       <c r="K5" s="98" t="n">
         <v>15</v>
       </c>
-      <c r="L5" s="94">
-        <f>K5</f>
-        <v/>
+      <c r="L5" s="94" t="n">
+        <v>15</v>
       </c>
       <c r="M5" s="52" t="n">
         <v>0</v>
@@ -1642,9 +1641,10 @@
       <c r="AE5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="71">
-        <f>A5</f>
-        <v/>
+      <c r="A6" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
@@ -1684,9 +1684,8 @@
       <c r="K6" s="98" t="n">
         <v>14.375</v>
       </c>
-      <c r="L6" s="94">
-        <f>K6</f>
-        <v/>
+      <c r="L6" s="94" t="n">
+        <v>14.375</v>
       </c>
       <c r="M6" s="52" t="n">
         <v>0</v>
@@ -1747,9 +1746,10 @@
       <c r="AE6" s="19" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="71">
-        <f>A6</f>
-        <v/>
+      <c r="A7" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
@@ -1789,9 +1789,8 @@
       <c r="K7" s="98" t="n">
         <v>14.32291666666667</v>
       </c>
-      <c r="L7" s="94">
-        <f>K7</f>
-        <v/>
+      <c r="L7" s="94" t="n">
+        <v>14.32291666666667</v>
       </c>
       <c r="M7" s="52" t="n">
         <v>0</v>
@@ -1852,9 +1851,10 @@
       <c r="AE7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="71">
-        <f>A7</f>
-        <v/>
+      <c r="A8" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
@@ -1894,9 +1894,8 @@
       <c r="K8" s="100" t="n">
         <v>12.29166666666667</v>
       </c>
-      <c r="L8" s="94">
-        <f>K8</f>
-        <v/>
+      <c r="L8" s="94" t="n">
+        <v>12.29166666666667</v>
       </c>
       <c r="M8" s="52" t="n">
         <v>0</v>
@@ -1957,9 +1956,10 @@
       <c r="AE8" s="35" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="71">
-        <f>A8</f>
-        <v/>
+      <c r="A9" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B9" s="44" t="inlineStr">
         <is>
@@ -1999,9 +1999,8 @@
       <c r="K9" s="100" t="n">
         <v>11.45833333333333</v>
       </c>
-      <c r="L9" s="94">
-        <f>K9</f>
-        <v/>
+      <c r="L9" s="94" t="n">
+        <v>11.45833333333333</v>
       </c>
       <c r="M9" s="52" t="n">
         <v>0</v>
@@ -2062,9 +2061,10 @@
       <c r="AE9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="71">
-        <f>A9</f>
-        <v/>
+      <c r="A10" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B10" s="45" t="inlineStr">
         <is>
@@ -2104,9 +2104,8 @@
       <c r="K10" s="98" t="n">
         <v>12.8125</v>
       </c>
-      <c r="L10" s="94">
-        <f>K10</f>
-        <v/>
+      <c r="L10" s="94" t="n">
+        <v>12.8125</v>
       </c>
       <c r="M10" s="52" t="n">
         <v>0</v>
@@ -2167,9 +2166,10 @@
       <c r="AE10" s="19" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="71">
-        <f>A10</f>
-        <v/>
+      <c r="A11" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B11" s="46" t="inlineStr">
         <is>
@@ -2209,9 +2209,8 @@
       <c r="K11" s="100" t="n">
         <v>10.41666666666667</v>
       </c>
-      <c r="L11" s="94">
-        <f>K11</f>
-        <v/>
+      <c r="L11" s="94" t="n">
+        <v>10.41666666666667</v>
       </c>
       <c r="M11" s="52" t="n">
         <v>0</v>
@@ -2272,9 +2271,10 @@
       <c r="AE11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="71">
-        <f>A11</f>
-        <v/>
+      <c r="A12" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B12" s="47" t="inlineStr">
         <is>
@@ -2314,9 +2314,8 @@
       <c r="K12" s="98" t="n">
         <v>11.25</v>
       </c>
-      <c r="L12" s="94">
-        <f>K12</f>
-        <v/>
+      <c r="L12" s="94" t="n">
+        <v>11.25</v>
       </c>
       <c r="M12" s="52" t="n">
         <v>0</v>
@@ -2377,9 +2376,10 @@
       <c r="AE12" s="19" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="71">
-        <f>A12</f>
-        <v/>
+      <c r="A13" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B13" s="48" t="inlineStr">
         <is>
@@ -2419,9 +2419,8 @@
       <c r="K13" s="98" t="n">
         <v>13.02083333333333</v>
       </c>
-      <c r="L13" s="94">
-        <f>K13</f>
-        <v/>
+      <c r="L13" s="94" t="n">
+        <v>13.02083333333333</v>
       </c>
       <c r="M13" s="52" t="n">
         <v>0</v>
@@ -2482,9 +2481,10 @@
       <c r="AE13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="71">
-        <f>A13</f>
-        <v/>
+      <c r="A14" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B14" s="53" t="inlineStr">
         <is>
@@ -2524,9 +2524,8 @@
       <c r="K14" s="98" t="n">
         <v>10.3125</v>
       </c>
-      <c r="L14" s="94">
-        <f>K14</f>
-        <v/>
+      <c r="L14" s="94" t="n">
+        <v>10.3125</v>
       </c>
       <c r="M14" s="52" t="n">
         <v>0</v>
@@ -2587,9 +2586,10 @@
       <c r="AE14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="71">
-        <f>A14</f>
-        <v/>
+      <c r="A15" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
@@ -2629,9 +2629,8 @@
       <c r="K15" s="100" t="n">
         <v>12.39583333333333</v>
       </c>
-      <c r="L15" s="94">
-        <f>K15</f>
-        <v/>
+      <c r="L15" s="94" t="n">
+        <v>12.39583333333333</v>
       </c>
       <c r="M15" s="52" t="n">
         <v>0</v>
@@ -2692,9 +2691,10 @@
       <c r="AE15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="71">
-        <f>A15</f>
-        <v/>
+      <c r="A16" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
@@ -2734,9 +2734,8 @@
       <c r="K16" s="100" t="n">
         <v>9.583333333333334</v>
       </c>
-      <c r="L16" s="94">
-        <f>K16</f>
-        <v/>
+      <c r="L16" s="94" t="n">
+        <v>9.583333333333334</v>
       </c>
       <c r="M16" s="52" t="n">
         <v>0</v>
@@ -2797,9 +2796,10 @@
       <c r="AE16" s="19" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="71">
-        <f>A16</f>
-        <v/>
+      <c r="A17" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
@@ -2839,9 +2839,8 @@
       <c r="K17" s="100" t="n">
         <v>12.8125</v>
       </c>
-      <c r="L17" s="94">
-        <f>K17</f>
-        <v/>
+      <c r="L17" s="94" t="n">
+        <v>12.8125</v>
       </c>
       <c r="M17" s="52" t="n">
         <v>0</v>
@@ -2902,9 +2901,10 @@
       <c r="AE17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="71">
-        <f>A17</f>
-        <v/>
+      <c r="A18" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
@@ -2944,9 +2944,8 @@
       <c r="K18" s="98" t="n">
         <v>11.111</v>
       </c>
-      <c r="L18" s="94">
-        <f>K18</f>
-        <v/>
+      <c r="L18" s="94" t="n">
+        <v>11.111</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
@@ -3005,9 +3004,10 @@
       <c r="AE18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="71">
-        <f>A18</f>
-        <v/>
+      <c r="A19" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
@@ -3047,9 +3047,8 @@
       <c r="K19" s="100" t="n">
         <v>11.519</v>
       </c>
-      <c r="L19" s="94">
-        <f>K19</f>
-        <v/>
+      <c r="L19" s="94" t="n">
+        <v>11.519</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -3114,9 +3113,10 @@
       <c r="AE19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="71">
-        <f>A19</f>
-        <v/>
+      <c r="A20" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
@@ -3156,9 +3156,8 @@
       <c r="K20" s="98" t="n">
         <v>11.519</v>
       </c>
-      <c r="L20" s="94">
-        <f>K20</f>
-        <v/>
+      <c r="L20" s="94" t="n">
+        <v>11.519</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -3223,9 +3222,10 @@
       <c r="AE20" s="19" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="71">
-        <f>A20</f>
-        <v/>
+      <c r="A21" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
@@ -3265,9 +3265,8 @@
       <c r="K21" s="100" t="n">
         <v>11.519</v>
       </c>
-      <c r="L21" s="94">
-        <f>K21</f>
-        <v/>
+      <c r="L21" s="94" t="n">
+        <v>11.519</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -3332,9 +3331,10 @@
       <c r="AE21" s="35" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="71">
-        <f>A21</f>
-        <v/>
+      <c r="A22" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B22" s="28" t="inlineStr">
         <is>
@@ -3374,9 +3374,8 @@
       <c r="K22" s="98" t="n">
         <v>11.519</v>
       </c>
-      <c r="L22" s="94">
-        <f>K22</f>
-        <v/>
+      <c r="L22" s="94" t="n">
+        <v>11.519</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
@@ -3441,9 +3440,10 @@
       <c r="AE22" s="19" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="71">
-        <f>A22</f>
-        <v/>
+      <c r="A23" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
@@ -3485,9 +3485,8 @@
       <c r="K23" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="94">
-        <f>K23</f>
-        <v/>
+      <c r="L23" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -3546,9 +3545,10 @@
       <c r="AE23" s="35" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="71">
-        <f>A23</f>
-        <v/>
+      <c r="A24" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
@@ -3590,9 +3590,8 @@
       <c r="K24" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="94">
-        <f>K24</f>
-        <v/>
+      <c r="L24" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -3651,9 +3650,10 @@
       <c r="AE24" s="19" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="71">
-        <f>A24</f>
-        <v/>
+      <c r="A25" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
@@ -3691,9 +3691,8 @@
       <c r="K25" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="94">
-        <f>K25</f>
-        <v/>
+      <c r="L25" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>0</v>
@@ -3752,9 +3751,10 @@
       <c r="AE25" s="19" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="71">
-        <f>A25</f>
-        <v/>
+      <c r="A26" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
@@ -3792,9 +3792,8 @@
       <c r="K26" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="94">
-        <f>K26</f>
-        <v/>
+      <c r="L26" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>0</v>
@@ -3853,9 +3852,10 @@
       <c r="AE26" s="35" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="71">
-        <f>A26</f>
-        <v/>
+      <c r="A27" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
@@ -3893,9 +3893,8 @@
       <c r="K27" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="94">
-        <f>K27</f>
-        <v/>
+      <c r="L27" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>0</v>
@@ -3954,9 +3953,10 @@
       <c r="AE27" s="19" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="71">
-        <f>A27</f>
-        <v/>
+      <c r="A28" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
@@ -3994,9 +3994,8 @@
       <c r="K28" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="94">
-        <f>K28</f>
-        <v/>
+      <c r="L28" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>0</v>
@@ -4055,9 +4054,10 @@
       <c r="AE28" s="35" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="71">
-        <f>A28</f>
-        <v/>
+      <c r="A29" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
@@ -4095,9 +4095,8 @@
       <c r="K29" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="94">
-        <f>K29</f>
-        <v/>
+      <c r="L29" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>0</v>
@@ -4156,9 +4155,10 @@
       <c r="AE29" s="19" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="71">
-        <f>A29</f>
-        <v/>
+      <c r="A30" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
@@ -4196,9 +4196,8 @@
       <c r="K30" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="94">
-        <f>K30</f>
-        <v/>
+      <c r="L30" s="94" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
@@ -4257,9 +4256,10 @@
       <c r="AE30" s="35" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="71">
-        <f>A30</f>
-        <v/>
+      <c r="A31" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
@@ -4299,9 +4299,8 @@
       <c r="K31" s="98" t="n">
         <v>11.519</v>
       </c>
-      <c r="L31" s="94">
-        <f>K31</f>
-        <v/>
+      <c r="L31" s="94" t="n">
+        <v>11.519</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
@@ -4366,9 +4365,10 @@
       <c r="AE31" s="19" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="71">
-        <f>A31</f>
-        <v/>
+      <c r="A32" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
@@ -4408,9 +4408,8 @@
       <c r="K32" s="100" t="n">
         <v>11.519</v>
       </c>
-      <c r="L32" s="94">
-        <f>K32</f>
-        <v/>
+      <c r="L32" s="94" t="n">
+        <v>11.519</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>0</v>
@@ -4475,9 +4474,10 @@
       <c r="AE32" s="35" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="71">
-        <f>A32</f>
-        <v/>
+      <c r="A33" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
@@ -4517,9 +4517,8 @@
       <c r="K33" s="98" t="n">
         <v>14.03125</v>
       </c>
-      <c r="L33" s="94">
-        <f>K33</f>
-        <v/>
+      <c r="L33" s="94" t="n">
+        <v>14.03125</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>0</v>
@@ -4578,9 +4577,10 @@
       <c r="AE33" s="19" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="71">
-        <f>A33</f>
-        <v/>
+      <c r="A34" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
@@ -4616,9 +4616,8 @@
       <c r="K34" s="100" t="n">
         <v>14.03125</v>
       </c>
-      <c r="L34" s="94">
-        <f>K34</f>
-        <v/>
+      <c r="L34" s="94" t="n">
+        <v>14.03125</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
@@ -4677,9 +4676,10 @@
       <c r="AE34" s="35" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="71">
-        <f>A34</f>
-        <v/>
+      <c r="A35" s="71" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
@@ -4719,9 +4719,8 @@
       <c r="K35" s="98" t="n">
         <v>9.6</v>
       </c>
-      <c r="L35" s="94">
-        <f>K35</f>
-        <v/>
+      <c r="L35" s="94" t="n">
+        <v>9.6</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>0</v>
@@ -4780,9 +4779,10 @@
       <c r="AE35" s="19" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="72">
-        <f>A35</f>
-        <v/>
+      <c r="A36" s="72" t="inlineStr">
+        <is>
+          <t>BASE_PMR1b</t>
+        </is>
       </c>
       <c r="B36" s="56" t="inlineStr">
         <is>
@@ -4822,9 +4822,8 @@
       <c r="K36" s="104" t="n">
         <v>9.6</v>
       </c>
-      <c r="L36" s="105">
-        <f>K36</f>
-        <v/>
+      <c r="L36" s="105" t="n">
+        <v>9.6</v>
       </c>
       <c r="M36" s="104" t="n">
         <v>0</v>
@@ -12389,9 +12388,8 @@
       <c r="K2" s="19" t="n">
         <v>21.7</v>
       </c>
-      <c r="L2" s="83">
-        <f>K2/E2*1000</f>
-        <v/>
+      <c r="L2" s="83" t="n">
+        <v>21.7</v>
       </c>
       <c r="M2" s="96" t="n">
         <v>-28.56283</v>
@@ -12401,9 +12399,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81">
-        <f>A2</f>
-        <v/>
+      <c r="A3" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -12445,9 +12444,8 @@
       <c r="K3" s="55" t="n">
         <v>27.4</v>
       </c>
-      <c r="L3" s="85">
-        <f>K3/E3*1000</f>
-        <v/>
+      <c r="L3" s="85" t="n">
+        <v>20.69486404833837</v>
       </c>
       <c r="M3" s="55" t="n">
         <v>-28.165</v>
@@ -12457,9 +12455,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="81">
-        <f>A3</f>
-        <v/>
+      <c r="A4" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
@@ -12501,9 +12500,8 @@
       <c r="K4" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="54">
-        <f>K4/E4*1000</f>
-        <v/>
+      <c r="L4" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="M4" s="54" t="n">
         <v>-34.19722</v>
@@ -12513,9 +12511,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="81">
-        <f>A4</f>
-        <v/>
+      <c r="A5" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
@@ -12557,9 +12556,8 @@
       <c r="K5" s="55" t="n">
         <v>2.7</v>
       </c>
-      <c r="L5" s="55">
-        <f>K5/E5*1000</f>
-        <v/>
+      <c r="L5" s="55" t="n">
+        <v>15</v>
       </c>
       <c r="M5" s="55" t="n">
         <v>-34.153</v>
@@ -12569,9 +12567,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="81">
-        <f>A5</f>
-        <v/>
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
@@ -12622,9 +12621,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="81">
-        <f>A6</f>
-        <v/>
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
@@ -12675,9 +12675,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="81">
-        <f>A7</f>
-        <v/>
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
@@ -12728,9 +12729,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="81">
-        <f>A8</f>
-        <v/>
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
@@ -12781,9 +12783,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="81">
-        <f>A9</f>
-        <v/>
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
@@ -12834,9 +12837,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="81">
-        <f>A10</f>
-        <v/>
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
@@ -12887,9 +12891,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="81">
-        <f>A11</f>
-        <v/>
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
@@ -12940,9 +12945,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="81">
-        <f>A12</f>
-        <v/>
+      <c r="A13" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
@@ -12993,9 +12999,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="81">
-        <f>A13</f>
-        <v/>
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
@@ -13046,9 +13053,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="81">
-        <f>A14</f>
-        <v/>
+      <c r="A15" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
@@ -13099,9 +13107,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="81">
-        <f>A15</f>
-        <v/>
+      <c r="A16" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
@@ -13152,9 +13161,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="81">
-        <f>A16</f>
-        <v/>
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
@@ -13205,9 +13215,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="81">
-        <f>A17</f>
-        <v/>
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
@@ -13258,9 +13269,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="81">
-        <f>A18</f>
-        <v/>
+      <c r="A19" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
@@ -13311,9 +13323,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="81">
-        <f>A19</f>
-        <v/>
+      <c r="A20" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
@@ -13364,9 +13377,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="81">
-        <f>A20</f>
-        <v/>
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
@@ -13417,9 +13431,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="81">
-        <f>A21</f>
-        <v/>
+      <c r="A22" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B22" s="28" t="inlineStr">
         <is>
@@ -13470,9 +13485,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="81">
-        <f>A22</f>
-        <v/>
+      <c r="A23" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
@@ -13523,9 +13539,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="81">
-        <f>A23</f>
-        <v/>
+      <c r="A24" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
@@ -13577,9 +13594,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="81">
-        <f>A24</f>
-        <v/>
+      <c r="A25" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
@@ -13631,9 +13649,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="81">
-        <f>A25</f>
-        <v/>
+      <c r="A26" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
@@ -13685,9 +13704,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="81">
-        <f>A26</f>
-        <v/>
+      <c r="A27" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
@@ -13739,9 +13759,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="81">
-        <f>A27</f>
-        <v/>
+      <c r="A28" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
@@ -13793,9 +13814,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="81">
-        <f>A28</f>
-        <v/>
+      <c r="A29" s="81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
@@ -13847,9 +13869,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="89">
-        <f>A28</f>
-        <v/>
+      <c r="A30" s="89" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
@@ -13901,9 +13924,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="89">
-        <f>A29</f>
-        <v/>
+      <c r="A31" s="89" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>

--- a/scenarios/Coal_Flexibilisation/sub_scenarios/fixed_technologies.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/fixed_technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_A95C29DBB4BACFB4F4360244DA388658F8CC5B57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{039019F7-649D-46BD-A6CC-7D4AD213825E}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_A95C29DBB4BACFB4F4360244DA388658F8CC5B57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD999BE2-65DA-41BF-ADF9-795C221B2E01}"/>
   <bookViews>
-    <workbookView xWindow="11070" yWindow="-15915" windowWidth="17880" windowHeight="15465" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6705" yWindow="-15540" windowWidth="17880" windowHeight="15465" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="conventional" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="340">
   <si>
     <t>scenario</t>
   </si>
@@ -1060,9 +1060,6 @@
   </si>
   <si>
     <t>Sappi</t>
-  </si>
-  <si>
-    <t>formula - L*E/1000</t>
   </si>
 </sst>
 </file>
@@ -1746,6 +1743,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2085,7 +2086,7 @@
         <v>13.54166666666667</v>
       </c>
       <c r="L2" s="51">
-        <f t="shared" ref="L2:L36" si="0">K2</f>
+        <f t="shared" ref="L2:L4" si="0">K2</f>
         <v>13.54166666666667</v>
       </c>
       <c r="M2" s="52">
@@ -10849,7 +10850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -12217,7 +12218,7 @@
         <v>20.03</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="78" t="s">
         <v>14</v>
       </c>
@@ -12260,11 +12261,6 @@
       </c>
       <c r="N31" s="43">
         <v>29.474460000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K33" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
   </sheetData>
